--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568489017</v>
+        <v>46157.93098170751</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93098170751</v>
+        <v>46157.93173271487</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93173271487</v>
+        <v>46157.93400327602</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400327602</v>
+        <v>46157.93718189929</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718189929</v>
+        <v>46158.28216518814</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216518814</v>
+        <v>46158.2968182254</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2968182254</v>
+        <v>46158.29814912044</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814912044</v>
+        <v>46158.33387588872</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387588872</v>
+        <v>46158.36857350462</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/7. ООО Альтернатива (СТО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857350462</v>
+        <v>46158.37288018259</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
